--- a/sample-data/plan.xlsx
+++ b/sample-data/plan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Исследование рынка</t>
+          <t>Исследование и бриф</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Анализ рынка мобильных приложений и целевой аудитории</t>
+          <t>Сбор требований, анализ конкурентов, подготовка брифа на лендинг</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -460,140 +460,144 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Анализ конкурентов</t>
+          <t>Дизайн лендинга</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Изучение конкурентных приложений и их фич</t>
+          <t>Визуальная концепция и макеты ключевых экранов</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Исследование и бриф</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Дизайн-концепция</t>
+          <t>Backend и форма заявки</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Формирование общей визуальной концепции продукта</t>
+          <t>API приёма заявок, интеграция с CRM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Исследование рынка, Анализ конкурентов</t>
+          <t>Исследование и бриф</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UI-кит</t>
+          <t>Тексты и контент</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Создание библиотеки UI-компонентов</t>
+          <t>Подготовка текстов, изображений и SEO-разметки по макетам</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Мария</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Дизайн-концепция</t>
+          <t>Дизайн лендинга</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Прототип</t>
+          <t>Вёрстка и интеграция</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Кликабельный прототип ключевых экранов</t>
+          <t>Вёрстка страницы по дизайну и подключение к backend-API</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Олег</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UI-кит</t>
+          <t>Дизайн лендинга, Backend и форма заявки</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Дизайн экранов онбординга</t>
+          <t>QA и тестирование</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Проработка экранов первого запуска приложения</t>
+          <t>Функциональное и кроссбраузерное тестирование перед запуском</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Олег</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Прототип</t>
+          <t>Вёрстка и интеграция, Тексты и контент</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Дизайн экрана профиля</t>
+          <t>Запуск и мониторинг</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Проработка экрана профиля пользователя</t>
+          <t>Публикация лендинга и мониторинг метрик после запуска</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -606,507 +610,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Прототип</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Архитектура backend</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Проектирование серверной архитектуры</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Дизайн-концепция</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>API авторизация</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Разработка API авторизации и аутентификации пользователей</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Архитектура backend</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>API платежи</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Разработка API для обработки платежей</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Архитектура backend</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>API push-уведомлений</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Разработка API отправки push-уведомлений</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Архитектура backend</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Интеграция платежей</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Интеграция с внешним платёжным провайдером</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>API платежи</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Интеграция аналитики</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Подключение системы аналитики событий</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Архитектура backend</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Разработка iOS-клиента</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Базовая разработка приложения под iOS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>API авторизация, Дизайн экранов онбординга, Дизайн экрана профиля</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Разработка Android-клиента</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Базовая разработка приложения под Android</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>API авторизация, Дизайн экранов онбординга, Дизайн экрана профиля</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Экран онбординга (frontend)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Реализация экрана онбординга в клиентском приложении</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Разработка iOS-клиента</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Пуш-уведомления (frontend)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Реализация приёма push-уведомлений в клиенте</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Разработка Android-клиента, API push-уведомлений</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Оплата в приложении (frontend)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Интеграция платёжного экрана в клиентское приложение</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Разработка iOS-клиента, Интеграция платежей</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit-тесты</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Написание модульных тестов backend и клиентов</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Экран онбординга (frontend), Пуш-уведомления (frontend)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>QA-регресс</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Полное регрессионное тестирование приложения</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Мария</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unit-тесты, Оплата в приложении (frontend)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Багфиксинг</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Исправление дефектов, найденных на QA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>QA-регресс</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Подготовка сторов</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Подготовка карточек и материалов для магазинов приложений</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Анна</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Багфиксинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Публикация в App Store</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Публикация релизной сборки в Apple App Store</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Подготовка сторов</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Публикация в Google Play</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Публикация релизной сборки в Google Play</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Подготовка сторов</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Маркетинговые материалы</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Подготовка рекламных материалов к запуску</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Мария</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Дизайн-концепция</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Пресс-релиз</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Подготовка и рассылка пресс-релиза о запуске</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Мария</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Маркетинговые материалы</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Пострелизный мониторинг</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Мониторинг стабильности и метрик после релиза</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Публикация в App Store, Публикация в Google Play, Пресс-релиз</t>
+          <t>QA и тестирование</t>
         </is>
       </c>
     </row>
